--- a/assets/银行对账单.xlsx
+++ b/assets/银行对账单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>账户主体</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>Transaction Description</t>
+  </si>
+  <si>
+    <t>合并单号</t>
+  </si>
+  <si>
+    <t>合并状态</t>
   </si>
   <si>
     <t>Extra Information</t>
@@ -1318,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="15.71875" customWidth="1"/>
@@ -1326,20 +1332,20 @@
     <col min="4" max="9" width="15.71875" customWidth="1"/>
     <col min="10" max="14" width="20.71875" customWidth="1"/>
     <col min="15" max="15" width="15.71875" customWidth="1"/>
-    <col min="16" max="18" width="20.71875" customWidth="1"/>
-    <col min="19" max="22" width="15.71875" customWidth="1"/>
-    <col min="23" max="24" width="20.71875" customWidth="1"/>
-    <col min="25" max="28" width="15.71875" customWidth="1"/>
-    <col min="29" max="29" width="20.71875" customWidth="1"/>
-    <col min="30" max="33" width="15.71875" customWidth="1"/>
-    <col min="34" max="34" width="20.71875" customWidth="1"/>
-    <col min="35" max="35" width="15.71875" customWidth="1"/>
-    <col min="36" max="37" width="20.71875" customWidth="1"/>
-    <col min="38" max="38" width="15.71875" customWidth="1"/>
-    <col min="39" max="44" width="20.71875" customWidth="1"/>
+    <col min="16" max="20" width="20.71875" customWidth="1"/>
+    <col min="21" max="24" width="15.71875" customWidth="1"/>
+    <col min="25" max="26" width="20.71875" customWidth="1"/>
+    <col min="27" max="30" width="15.71875" customWidth="1"/>
+    <col min="31" max="31" width="20.71875" customWidth="1"/>
+    <col min="32" max="35" width="15.71875" customWidth="1"/>
+    <col min="36" max="36" width="20.71875" customWidth="1"/>
+    <col min="37" max="37" width="15.71875" customWidth="1"/>
+    <col min="38" max="39" width="20.71875" customWidth="1"/>
+    <col min="40" max="40" width="15.71875" customWidth="1"/>
+    <col min="41" max="46" width="20.71875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:46">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1471,6 +1477,12 @@
       </c>
       <c r="AR1" t="s">
         <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
